--- a/news_daily/2026-08-14.xlsx
+++ b/news_daily/2026-08-14.xlsx
@@ -2270,28 +2270,32 @@
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -2335,7 +2339,7 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
@@ -2344,7 +2348,11 @@
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr"/>
-      <c r="AB9" s="3" t="inlineStr"/>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>2cf0ab62a00f4ecb82460f44acd0c373</t>
+        </is>
+      </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
           <t>7f6bd5cb477f1c3da69a1897</t>
@@ -2365,7 +2373,11 @@
       <c r="AL9" s="3" t="inlineStr"/>
       <c r="AM9" s="3" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="3" t="inlineStr"/>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr"/>
@@ -2409,10 +2421,22 @@
         </is>
       </c>
       <c r="BH9" s="3" t="inlineStr"/>
-      <c r="BI9" s="3" t="inlineStr"/>
+      <c r="BI9" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ9" s="3" t="inlineStr"/>
-      <c r="BK9" s="3" t="inlineStr"/>
-      <c r="BL9" s="3" t="inlineStr"/>
+      <c r="BK9" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -3984,28 +4008,32 @@
       <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -4049,7 +4077,7 @@
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
@@ -4058,7 +4086,11 @@
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr"/>
-      <c r="AB18" s="3" t="inlineStr"/>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>548574cad56f4922971bc3b5ae4c5525</t>
+        </is>
+      </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
           <t>457f581f41d99ca06e15b788</t>
@@ -4079,7 +4111,11 @@
       <c r="AL18" s="3" t="inlineStr"/>
       <c r="AM18" s="3" t="inlineStr"/>
       <c r="AN18" s="3" t="inlineStr"/>
-      <c r="AO18" s="3" t="inlineStr"/>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP18" s="3" t="inlineStr"/>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr"/>
@@ -4123,10 +4159,22 @@
         </is>
       </c>
       <c r="BH18" s="3" t="inlineStr"/>
-      <c r="BI18" s="3" t="inlineStr"/>
+      <c r="BI18" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ18" s="3" t="inlineStr"/>
-      <c r="BK18" s="3" t="inlineStr"/>
-      <c r="BL18" s="3" t="inlineStr"/>
+      <c r="BK18" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL18" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4546,28 +4594,32 @@
       <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -4611,7 +4663,7 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
@@ -4620,7 +4672,11 @@
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr"/>
-      <c r="AB21" s="3" t="inlineStr"/>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>95e087f0e6b94ace91dab5a2ecab3af6</t>
+        </is>
+      </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
           <t>2a4c7101cd9f0c8b3e620ab2</t>
@@ -4641,7 +4697,11 @@
       <c r="AL21" s="3" t="inlineStr"/>
       <c r="AM21" s="3" t="inlineStr"/>
       <c r="AN21" s="3" t="inlineStr"/>
-      <c r="AO21" s="3" t="inlineStr"/>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP21" s="3" t="inlineStr"/>
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr"/>
@@ -4685,10 +4745,22 @@
         </is>
       </c>
       <c r="BH21" s="3" t="inlineStr"/>
-      <c r="BI21" s="3" t="inlineStr"/>
+      <c r="BI21" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ21" s="3" t="inlineStr"/>
-      <c r="BK21" s="3" t="inlineStr"/>
-      <c r="BL21" s="3" t="inlineStr"/>
+      <c r="BK21" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL21" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -4724,28 +4796,32 @@
       <c r="G22" s="3" t="inlineStr"/>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -4789,7 +4865,7 @@
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
@@ -4798,7 +4874,11 @@
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr"/>
-      <c r="AB22" s="3" t="inlineStr"/>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>02a62dc1d9b94d078b83aa88d1852ef7</t>
+        </is>
+      </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
           <t>a003a08d76b6db8e33dd8cc6</t>
@@ -4819,7 +4899,11 @@
       <c r="AL22" s="3" t="inlineStr"/>
       <c r="AM22" s="3" t="inlineStr"/>
       <c r="AN22" s="3" t="inlineStr"/>
-      <c r="AO22" s="3" t="inlineStr"/>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP22" s="3" t="inlineStr"/>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr"/>
@@ -4855,10 +4939,22 @@
         </is>
       </c>
       <c r="BH22" s="3" t="inlineStr"/>
-      <c r="BI22" s="3" t="inlineStr"/>
+      <c r="BI22" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ22" s="3" t="inlineStr"/>
-      <c r="BK22" s="3" t="inlineStr"/>
-      <c r="BL22" s="3" t="inlineStr"/>
+      <c r="BK22" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL22" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -5880,28 +5976,32 @@
       <c r="G28" s="3" t="inlineStr"/>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -5945,7 +6045,7 @@
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
@@ -5954,7 +6054,11 @@
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr"/>
-      <c r="AB28" s="3" t="inlineStr"/>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>7e5d50fe9cd64d449508a12b2a7d50a1</t>
+        </is>
+      </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
           <t>49af640e4d579d2b585d0f8f</t>
@@ -5975,7 +6079,11 @@
       <c r="AL28" s="3" t="inlineStr"/>
       <c r="AM28" s="3" t="inlineStr"/>
       <c r="AN28" s="3" t="inlineStr"/>
-      <c r="AO28" s="3" t="inlineStr"/>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP28" s="3" t="inlineStr"/>
       <c r="AQ28" s="3" t="inlineStr"/>
       <c r="AR28" s="3" t="inlineStr"/>
@@ -6011,10 +6119,22 @@
         </is>
       </c>
       <c r="BH28" s="3" t="inlineStr"/>
-      <c r="BI28" s="3" t="inlineStr"/>
+      <c r="BI28" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ28" s="3" t="inlineStr"/>
-      <c r="BK28" s="3" t="inlineStr"/>
-      <c r="BL28" s="3" t="inlineStr"/>
+      <c r="BK28" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL28" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -8564,28 +8684,32 @@
       <c r="G42" s="3" t="inlineStr"/>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -8629,7 +8753,7 @@
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
@@ -8638,7 +8762,11 @@
         </is>
       </c>
       <c r="AA42" s="3" t="inlineStr"/>
-      <c r="AB42" s="3" t="inlineStr"/>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>33265cde9e3e46349126a3b7a8e096f0</t>
+        </is>
+      </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
           <t>6ab31b396cc4d479f0c3123b</t>
@@ -8659,7 +8787,11 @@
       <c r="AL42" s="3" t="inlineStr"/>
       <c r="AM42" s="3" t="inlineStr"/>
       <c r="AN42" s="3" t="inlineStr"/>
-      <c r="AO42" s="3" t="inlineStr"/>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP42" s="3" t="inlineStr"/>
       <c r="AQ42" s="3" t="inlineStr"/>
       <c r="AR42" s="3" t="inlineStr"/>
@@ -8703,10 +8835,22 @@
         </is>
       </c>
       <c r="BH42" s="3" t="inlineStr"/>
-      <c r="BI42" s="3" t="inlineStr"/>
+      <c r="BI42" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ42" s="3" t="inlineStr"/>
-      <c r="BK42" s="3" t="inlineStr"/>
-      <c r="BL42" s="3" t="inlineStr"/>
+      <c r="BK42" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL42" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -9126,28 +9270,32 @@
       <c r="G45" s="3" t="inlineStr"/>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
@@ -9191,7 +9339,7 @@
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
@@ -9200,7 +9348,11 @@
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr"/>
-      <c r="AB45" s="3" t="inlineStr"/>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>f8f84fbc43764fca9c4df7052abcde1c</t>
+        </is>
+      </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
           <t>8d3b26df9b8429cf351fd6d4</t>
@@ -9221,7 +9373,11 @@
       <c r="AL45" s="3" t="inlineStr"/>
       <c r="AM45" s="3" t="inlineStr"/>
       <c r="AN45" s="3" t="inlineStr"/>
-      <c r="AO45" s="3" t="inlineStr"/>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP45" s="3" t="inlineStr"/>
       <c r="AQ45" s="3" t="inlineStr"/>
       <c r="AR45" s="3" t="inlineStr"/>
@@ -9265,10 +9421,22 @@
         </is>
       </c>
       <c r="BH45" s="3" t="inlineStr"/>
-      <c r="BI45" s="3" t="inlineStr"/>
+      <c r="BI45" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ45" s="3" t="inlineStr"/>
-      <c r="BK45" s="3" t="inlineStr"/>
-      <c r="BL45" s="3" t="inlineStr"/>
+      <c r="BK45" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL45" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -9304,28 +9472,32 @@
       <c r="G46" s="3" t="inlineStr"/>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -9369,7 +9541,7 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
@@ -9378,7 +9550,11 @@
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr"/>
-      <c r="AB46" s="3" t="inlineStr"/>
+      <c r="AB46" s="3" t="inlineStr">
+        <is>
+          <t>fb99cfb09341450bb775e523573011ff</t>
+        </is>
+      </c>
       <c r="AC46" s="3" t="inlineStr">
         <is>
           <t>e5c7e7344c9cead84b80c538</t>
@@ -9399,7 +9575,11 @@
       <c r="AL46" s="3" t="inlineStr"/>
       <c r="AM46" s="3" t="inlineStr"/>
       <c r="AN46" s="3" t="inlineStr"/>
-      <c r="AO46" s="3" t="inlineStr"/>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP46" s="3" t="inlineStr"/>
       <c r="AQ46" s="3" t="inlineStr"/>
       <c r="AR46" s="3" t="inlineStr"/>
@@ -9443,10 +9623,22 @@
         </is>
       </c>
       <c r="BH46" s="3" t="inlineStr"/>
-      <c r="BI46" s="3" t="inlineStr"/>
+      <c r="BI46" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ46" s="3" t="inlineStr"/>
-      <c r="BK46" s="3" t="inlineStr"/>
-      <c r="BL46" s="3" t="inlineStr"/>
+      <c r="BK46" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL46" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9676,28 +9868,32 @@
       <c r="G48" s="3" t="inlineStr"/>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L48" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
@@ -9741,7 +9937,7 @@
       </c>
       <c r="Y48" s="3" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z48" s="3" t="inlineStr">
@@ -9750,7 +9946,11 @@
         </is>
       </c>
       <c r="AA48" s="3" t="inlineStr"/>
-      <c r="AB48" s="3" t="inlineStr"/>
+      <c r="AB48" s="3" t="inlineStr">
+        <is>
+          <t>a9e378b5d89b43b39683e96d259bed32</t>
+        </is>
+      </c>
       <c r="AC48" s="3" t="inlineStr">
         <is>
           <t>9be4152a9c7455d838d31020</t>
@@ -9771,7 +9971,11 @@
       <c r="AL48" s="3" t="inlineStr"/>
       <c r="AM48" s="3" t="inlineStr"/>
       <c r="AN48" s="3" t="inlineStr"/>
-      <c r="AO48" s="3" t="inlineStr"/>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP48" s="3" t="inlineStr"/>
       <c r="AQ48" s="3" t="inlineStr"/>
       <c r="AR48" s="3" t="inlineStr"/>
@@ -9815,10 +10019,22 @@
         </is>
       </c>
       <c r="BH48" s="3" t="inlineStr"/>
-      <c r="BI48" s="3" t="inlineStr"/>
+      <c r="BI48" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ48" s="3" t="inlineStr"/>
-      <c r="BK48" s="3" t="inlineStr"/>
-      <c r="BL48" s="3" t="inlineStr"/>
+      <c r="BK48" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL48" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -9854,28 +10070,32 @@
       <c r="G49" s="3" t="inlineStr"/>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L49" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
@@ -9919,7 +10139,7 @@
       </c>
       <c r="Y49" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z49" s="3" t="inlineStr">
@@ -9928,7 +10148,11 @@
         </is>
       </c>
       <c r="AA49" s="3" t="inlineStr"/>
-      <c r="AB49" s="3" t="inlineStr"/>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>48717477622d4b40a4dd89441ae047a4</t>
+        </is>
+      </c>
       <c r="AC49" s="3" t="inlineStr">
         <is>
           <t>5404da934c3f74f3a9f4da61</t>
@@ -9949,7 +10173,11 @@
       <c r="AL49" s="3" t="inlineStr"/>
       <c r="AM49" s="3" t="inlineStr"/>
       <c r="AN49" s="3" t="inlineStr"/>
-      <c r="AO49" s="3" t="inlineStr"/>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP49" s="3" t="inlineStr"/>
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr"/>
@@ -9993,10 +10221,22 @@
         </is>
       </c>
       <c r="BH49" s="3" t="inlineStr"/>
-      <c r="BI49" s="3" t="inlineStr"/>
+      <c r="BI49" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ49" s="3" t="inlineStr"/>
-      <c r="BK49" s="3" t="inlineStr"/>
-      <c r="BL49" s="3" t="inlineStr"/>
+      <c r="BK49" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL49" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -10234,28 +10474,32 @@
       <c r="G51" s="3" t="inlineStr"/>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L51" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
@@ -10299,7 +10543,7 @@
       </c>
       <c r="Y51" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z51" s="3" t="inlineStr">
@@ -10308,7 +10552,11 @@
         </is>
       </c>
       <c r="AA51" s="3" t="inlineStr"/>
-      <c r="AB51" s="3" t="inlineStr"/>
+      <c r="AB51" s="3" t="inlineStr">
+        <is>
+          <t>18cf9eaad3154027b1cd55912c156d35</t>
+        </is>
+      </c>
       <c r="AC51" s="3" t="inlineStr">
         <is>
           <t>2bfc6b742aea98b77bc12f03</t>
@@ -10329,7 +10577,11 @@
       <c r="AL51" s="3" t="inlineStr"/>
       <c r="AM51" s="3" t="inlineStr"/>
       <c r="AN51" s="3" t="inlineStr"/>
-      <c r="AO51" s="3" t="inlineStr"/>
+      <c r="AO51" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP51" s="3" t="inlineStr"/>
       <c r="AQ51" s="3" t="inlineStr"/>
       <c r="AR51" s="3" t="inlineStr"/>
@@ -10373,10 +10625,22 @@
         </is>
       </c>
       <c r="BH51" s="3" t="inlineStr"/>
-      <c r="BI51" s="3" t="inlineStr"/>
+      <c r="BI51" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ51" s="3" t="inlineStr"/>
-      <c r="BK51" s="3" t="inlineStr"/>
-      <c r="BL51" s="3" t="inlineStr"/>
+      <c r="BK51" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL51" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -10412,28 +10676,32 @@
       <c r="G52" s="3" t="inlineStr"/>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L52" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
@@ -10477,7 +10745,7 @@
       </c>
       <c r="Y52" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z52" s="3" t="inlineStr">
@@ -10486,7 +10754,11 @@
         </is>
       </c>
       <c r="AA52" s="3" t="inlineStr"/>
-      <c r="AB52" s="3" t="inlineStr"/>
+      <c r="AB52" s="3" t="inlineStr">
+        <is>
+          <t>c70e2ce54d824f339288add366c07231</t>
+        </is>
+      </c>
       <c r="AC52" s="3" t="inlineStr">
         <is>
           <t>596d109d7e5f90d82f7f8bbe</t>
@@ -10507,7 +10779,11 @@
       <c r="AL52" s="3" t="inlineStr"/>
       <c r="AM52" s="3" t="inlineStr"/>
       <c r="AN52" s="3" t="inlineStr"/>
-      <c r="AO52" s="3" t="inlineStr"/>
+      <c r="AO52" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP52" s="3" t="inlineStr"/>
       <c r="AQ52" s="3" t="inlineStr"/>
       <c r="AR52" s="3" t="inlineStr"/>
@@ -10551,10 +10827,22 @@
         </is>
       </c>
       <c r="BH52" s="3" t="inlineStr"/>
-      <c r="BI52" s="3" t="inlineStr"/>
+      <c r="BI52" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ52" s="3" t="inlineStr"/>
-      <c r="BK52" s="3" t="inlineStr"/>
-      <c r="BL52" s="3" t="inlineStr"/>
+      <c r="BK52" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL52" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -10590,28 +10878,32 @@
       <c r="G53" s="3" t="inlineStr"/>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L53" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -10655,7 +10947,7 @@
       </c>
       <c r="Y53" s="3" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z53" s="3" t="inlineStr">
@@ -10664,7 +10956,11 @@
         </is>
       </c>
       <c r="AA53" s="3" t="inlineStr"/>
-      <c r="AB53" s="3" t="inlineStr"/>
+      <c r="AB53" s="3" t="inlineStr">
+        <is>
+          <t>2d719a301f9948a183e1d9114cc251f1</t>
+        </is>
+      </c>
       <c r="AC53" s="3" t="inlineStr">
         <is>
           <t>65ae959e969782a7ecda2beb</t>
@@ -10685,7 +10981,11 @@
       <c r="AL53" s="3" t="inlineStr"/>
       <c r="AM53" s="3" t="inlineStr"/>
       <c r="AN53" s="3" t="inlineStr"/>
-      <c r="AO53" s="3" t="inlineStr"/>
+      <c r="AO53" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP53" s="3" t="inlineStr"/>
       <c r="AQ53" s="3" t="inlineStr"/>
       <c r="AR53" s="3" t="inlineStr"/>
@@ -10729,10 +11029,22 @@
         </is>
       </c>
       <c r="BH53" s="3" t="inlineStr"/>
-      <c r="BI53" s="3" t="inlineStr"/>
+      <c r="BI53" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ53" s="3" t="inlineStr"/>
-      <c r="BK53" s="3" t="inlineStr"/>
-      <c r="BL53" s="3" t="inlineStr"/>
+      <c r="BK53" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL53" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -10768,28 +11080,32 @@
       <c r="G54" s="3" t="inlineStr"/>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L54" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
@@ -10833,7 +11149,7 @@
       </c>
       <c r="Y54" s="3" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z54" s="3" t="inlineStr">
@@ -10842,7 +11158,11 @@
         </is>
       </c>
       <c r="AA54" s="3" t="inlineStr"/>
-      <c r="AB54" s="3" t="inlineStr"/>
+      <c r="AB54" s="3" t="inlineStr">
+        <is>
+          <t>0ee4eb5851f14159aa17d938ef07f285</t>
+        </is>
+      </c>
       <c r="AC54" s="3" t="inlineStr">
         <is>
           <t>6e46d3112e6a0f2c59df429d</t>
@@ -10863,7 +11183,11 @@
       <c r="AL54" s="3" t="inlineStr"/>
       <c r="AM54" s="3" t="inlineStr"/>
       <c r="AN54" s="3" t="inlineStr"/>
-      <c r="AO54" s="3" t="inlineStr"/>
+      <c r="AO54" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP54" s="3" t="inlineStr"/>
       <c r="AQ54" s="3" t="inlineStr"/>
       <c r="AR54" s="3" t="inlineStr"/>
@@ -10907,10 +11231,22 @@
         </is>
       </c>
       <c r="BH54" s="3" t="inlineStr"/>
-      <c r="BI54" s="3" t="inlineStr"/>
+      <c r="BI54" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ54" s="3" t="inlineStr"/>
-      <c r="BK54" s="3" t="inlineStr"/>
-      <c r="BL54" s="3" t="inlineStr"/>
+      <c r="BK54" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL54" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -10946,28 +11282,32 @@
       <c r="G55" s="3" t="inlineStr"/>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L55" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
@@ -11011,7 +11351,7 @@
       </c>
       <c r="Y55" s="3" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z55" s="3" t="inlineStr">
@@ -11020,7 +11360,11 @@
         </is>
       </c>
       <c r="AA55" s="3" t="inlineStr"/>
-      <c r="AB55" s="3" t="inlineStr"/>
+      <c r="AB55" s="3" t="inlineStr">
+        <is>
+          <t>1a40489ecd90444ea0a036cfc8942291</t>
+        </is>
+      </c>
       <c r="AC55" s="3" t="inlineStr">
         <is>
           <t>9abdd080eabb7e9893bcd045</t>
@@ -11041,7 +11385,11 @@
       <c r="AL55" s="3" t="inlineStr"/>
       <c r="AM55" s="3" t="inlineStr"/>
       <c r="AN55" s="3" t="inlineStr"/>
-      <c r="AO55" s="3" t="inlineStr"/>
+      <c r="AO55" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP55" s="3" t="inlineStr"/>
       <c r="AQ55" s="3" t="inlineStr"/>
       <c r="AR55" s="3" t="inlineStr"/>
@@ -11085,10 +11433,22 @@
         </is>
       </c>
       <c r="BH55" s="3" t="inlineStr"/>
-      <c r="BI55" s="3" t="inlineStr"/>
+      <c r="BI55" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ55" s="3" t="inlineStr"/>
-      <c r="BK55" s="3" t="inlineStr"/>
-      <c r="BL55" s="3" t="inlineStr"/>
+      <c r="BK55" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL55" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -11698,28 +12058,32 @@
       <c r="G59" s="3" t="inlineStr"/>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L59" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
@@ -11763,7 +12127,7 @@
       </c>
       <c r="Y59" s="3" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z59" s="3" t="inlineStr">
@@ -11772,7 +12136,11 @@
         </is>
       </c>
       <c r="AA59" s="3" t="inlineStr"/>
-      <c r="AB59" s="3" t="inlineStr"/>
+      <c r="AB59" s="3" t="inlineStr">
+        <is>
+          <t>f6ec21ee4a1b44bd9877dea86d90bf5c</t>
+        </is>
+      </c>
       <c r="AC59" s="3" t="inlineStr">
         <is>
           <t>72b814d64b3cc86653fc5baa</t>
@@ -11793,7 +12161,11 @@
       <c r="AL59" s="3" t="inlineStr"/>
       <c r="AM59" s="3" t="inlineStr"/>
       <c r="AN59" s="3" t="inlineStr"/>
-      <c r="AO59" s="3" t="inlineStr"/>
+      <c r="AO59" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP59" s="3" t="inlineStr"/>
       <c r="AQ59" s="3" t="inlineStr"/>
       <c r="AR59" s="3" t="inlineStr"/>
@@ -11837,10 +12209,22 @@
         </is>
       </c>
       <c r="BH59" s="3" t="inlineStr"/>
-      <c r="BI59" s="3" t="inlineStr"/>
+      <c r="BI59" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ59" s="3" t="inlineStr"/>
-      <c r="BK59" s="3" t="inlineStr"/>
-      <c r="BL59" s="3" t="inlineStr"/>
+      <c r="BK59" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL59" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -13258,28 +13642,32 @@
       <c r="G67" s="3" t="inlineStr"/>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L67" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
@@ -13323,7 +13711,7 @@
       </c>
       <c r="Y67" s="3" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z67" s="3" t="inlineStr">
@@ -13332,7 +13720,11 @@
         </is>
       </c>
       <c r="AA67" s="3" t="inlineStr"/>
-      <c r="AB67" s="3" t="inlineStr"/>
+      <c r="AB67" s="3" t="inlineStr">
+        <is>
+          <t>33ef17373c664af0ad5184d27a610c0b</t>
+        </is>
+      </c>
       <c r="AC67" s="3" t="inlineStr">
         <is>
           <t>7a5512341eeb99eee4ada88c</t>
@@ -13353,7 +13745,11 @@
       <c r="AL67" s="3" t="inlineStr"/>
       <c r="AM67" s="3" t="inlineStr"/>
       <c r="AN67" s="3" t="inlineStr"/>
-      <c r="AO67" s="3" t="inlineStr"/>
+      <c r="AO67" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP67" s="3" t="inlineStr"/>
       <c r="AQ67" s="3" t="inlineStr"/>
       <c r="AR67" s="3" t="inlineStr"/>
@@ -13397,10 +13793,22 @@
         </is>
       </c>
       <c r="BH67" s="3" t="inlineStr"/>
-      <c r="BI67" s="3" t="inlineStr"/>
+      <c r="BI67" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ67" s="3" t="inlineStr"/>
-      <c r="BK67" s="3" t="inlineStr"/>
-      <c r="BL67" s="3" t="inlineStr"/>
+      <c r="BK67" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL67" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -13436,28 +13844,32 @@
       <c r="G68" s="3" t="inlineStr"/>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L68" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
@@ -13501,7 +13913,7 @@
       </c>
       <c r="Y68" s="3" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z68" s="3" t="inlineStr">
@@ -13510,7 +13922,11 @@
         </is>
       </c>
       <c r="AA68" s="3" t="inlineStr"/>
-      <c r="AB68" s="3" t="inlineStr"/>
+      <c r="AB68" s="3" t="inlineStr">
+        <is>
+          <t>1e098059c3774fae84553e14f049ed0c</t>
+        </is>
+      </c>
       <c r="AC68" s="3" t="inlineStr">
         <is>
           <t>84f265548b47af5261c24c90</t>
@@ -13531,7 +13947,11 @@
       <c r="AL68" s="3" t="inlineStr"/>
       <c r="AM68" s="3" t="inlineStr"/>
       <c r="AN68" s="3" t="inlineStr"/>
-      <c r="AO68" s="3" t="inlineStr"/>
+      <c r="AO68" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP68" s="3" t="inlineStr"/>
       <c r="AQ68" s="3" t="inlineStr"/>
       <c r="AR68" s="3" t="inlineStr"/>
@@ -13575,10 +13995,22 @@
         </is>
       </c>
       <c r="BH68" s="3" t="inlineStr"/>
-      <c r="BI68" s="3" t="inlineStr"/>
+      <c r="BI68" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ68" s="3" t="inlineStr"/>
-      <c r="BK68" s="3" t="inlineStr"/>
-      <c r="BL68" s="3" t="inlineStr"/>
+      <c r="BK68" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL68" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -13614,28 +14046,32 @@
       <c r="G69" s="3" t="inlineStr"/>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L69" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr">
@@ -13679,7 +14115,7 @@
       </c>
       <c r="Y69" s="3" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z69" s="3" t="inlineStr">
@@ -13688,7 +14124,11 @@
         </is>
       </c>
       <c r="AA69" s="3" t="inlineStr"/>
-      <c r="AB69" s="3" t="inlineStr"/>
+      <c r="AB69" s="3" t="inlineStr">
+        <is>
+          <t>3828044368544312b446b00b045535ae</t>
+        </is>
+      </c>
       <c r="AC69" s="3" t="inlineStr">
         <is>
           <t>832b53d3683d44852cd0fd1e</t>
@@ -13709,7 +14149,11 @@
       <c r="AL69" s="3" t="inlineStr"/>
       <c r="AM69" s="3" t="inlineStr"/>
       <c r="AN69" s="3" t="inlineStr"/>
-      <c r="AO69" s="3" t="inlineStr"/>
+      <c r="AO69" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP69" s="3" t="inlineStr"/>
       <c r="AQ69" s="3" t="inlineStr"/>
       <c r="AR69" s="3" t="inlineStr"/>
@@ -13753,10 +14197,22 @@
         </is>
       </c>
       <c r="BH69" s="3" t="inlineStr"/>
-      <c r="BI69" s="3" t="inlineStr"/>
+      <c r="BI69" s="3" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ69" s="3" t="inlineStr"/>
-      <c r="BK69" s="3" t="inlineStr"/>
-      <c r="BL69" s="3" t="inlineStr"/>
+      <c r="BK69" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL69" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
